--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A4AE94-2957-47D3-9514-3978CAD414A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA061A6-946C-4B51-B744-232C1BBA2C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
@@ -70284,10 +70284,10 @@
         <v>6108</v>
       </c>
       <c r="F1126" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1126" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1126" s="15">
         <v>0</v>
@@ -70344,10 +70344,10 @@
         <v>6108</v>
       </c>
       <c r="F1127" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1127" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1127" s="15">
         <v>0</v>
@@ -70404,10 +70404,10 @@
         <v>6108</v>
       </c>
       <c r="F1128" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1128" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1128" s="15">
         <v>0</v>
@@ -70464,10 +70464,10 @@
         <v>6108</v>
       </c>
       <c r="F1129" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1129" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1129" s="15">
         <v>0</v>
@@ -70524,10 +70524,10 @@
         <v>5102</v>
       </c>
       <c r="F1130" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1130" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1130" s="15">
         <v>0</v>
@@ -70584,10 +70584,10 @@
         <v>6108</v>
       </c>
       <c r="F1131" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1131" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1131" s="15">
         <v>0</v>
@@ -70644,10 +70644,10 @@
         <v>6108</v>
       </c>
       <c r="F1132" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1132" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1132" s="15">
         <v>0</v>
@@ -70704,10 +70704,10 @@
         <v>6108</v>
       </c>
       <c r="F1133" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1133" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1133" s="15">
         <v>0</v>
@@ -70764,10 +70764,10 @@
         <v>6108</v>
       </c>
       <c r="F1134" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1134" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1134" s="15">
         <v>0</v>
@@ -70824,10 +70824,10 @@
         <v>6108</v>
       </c>
       <c r="F1135" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1135" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1135" s="15">
         <v>0</v>
@@ -70884,10 +70884,10 @@
         <v>6108</v>
       </c>
       <c r="F1136" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1136" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1136" s="15">
         <v>0</v>
@@ -70944,10 +70944,10 @@
         <v>6108</v>
       </c>
       <c r="F1137" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1137" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1137" s="15">
         <v>0</v>
@@ -71004,10 +71004,10 @@
         <v>5102</v>
       </c>
       <c r="F1138" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1138" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1138" s="15">
         <v>0</v>
@@ -71064,10 +71064,10 @@
         <v>6108</v>
       </c>
       <c r="F1139" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1139" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1139" s="15">
         <v>0</v>
@@ -71124,10 +71124,10 @@
         <v>6108</v>
       </c>
       <c r="F1140" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1140" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1140" s="15">
         <v>0</v>
@@ -71184,10 +71184,10 @@
         <v>6108</v>
       </c>
       <c r="F1141" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1141" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1141" s="15">
         <v>0</v>
@@ -71244,10 +71244,10 @@
         <v>6108</v>
       </c>
       <c r="F1142" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1142" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1142" s="15">
         <v>0</v>
@@ -71304,10 +71304,10 @@
         <v>6108</v>
       </c>
       <c r="F1143" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1143" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1143" s="15">
         <v>0</v>
@@ -71364,10 +71364,10 @@
         <v>5102</v>
       </c>
       <c r="F1144" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1144" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1144" s="15">
         <v>0</v>
@@ -71424,10 +71424,10 @@
         <v>6108</v>
       </c>
       <c r="F1145" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1145" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1145" s="15">
         <v>0</v>
@@ -71484,10 +71484,10 @@
         <v>6108</v>
       </c>
       <c r="F1146" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1146" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1146" s="15">
         <v>0</v>
@@ -71544,10 +71544,10 @@
         <v>6108</v>
       </c>
       <c r="F1147" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1147" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1147" s="15">
         <v>0</v>
@@ -71604,10 +71604,10 @@
         <v>6108</v>
       </c>
       <c r="F1148" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1148" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1148" s="15">
         <v>0</v>
@@ -71664,10 +71664,10 @@
         <v>6108</v>
       </c>
       <c r="F1149" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1149" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1149" s="15">
         <v>0</v>
@@ -71724,10 +71724,10 @@
         <v>6108</v>
       </c>
       <c r="F1150" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1150" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1150" s="15">
         <v>0</v>
@@ -71784,10 +71784,10 @@
         <v>5102</v>
       </c>
       <c r="F1151" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1151" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1151" s="15">
         <v>0</v>
@@ -71842,10 +71842,10 @@
         <v>6108</v>
       </c>
       <c r="F1152" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1152" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1152" s="15">
         <v>0</v>
@@ -71902,10 +71902,10 @@
         <v>6108</v>
       </c>
       <c r="F1153" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1153" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1153" s="15">
         <v>0</v>
@@ -71962,10 +71962,10 @@
         <v>6108</v>
       </c>
       <c r="F1154" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1154" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1154" s="15">
         <v>0</v>
@@ -72022,10 +72022,10 @@
         <v>6108</v>
       </c>
       <c r="F1155" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1155" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1155" s="15">
         <v>0</v>
@@ -72082,10 +72082,10 @@
         <v>5102</v>
       </c>
       <c r="F1156" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1156" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1156" s="15">
         <v>0</v>
@@ -72142,10 +72142,10 @@
         <v>6108</v>
       </c>
       <c r="F1157" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1157" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1157" s="15">
         <v>0</v>
@@ -72202,10 +72202,10 @@
         <v>6108</v>
       </c>
       <c r="F1158" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1158" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1158" s="15">
         <v>0</v>
@@ -72262,10 +72262,10 @@
         <v>5405</v>
       </c>
       <c r="F1159" s="15">
-        <v>0</v>
+        <v>5405</v>
       </c>
       <c r="G1159" s="15">
-        <v>5405</v>
+        <v>0</v>
       </c>
       <c r="H1159" s="15">
         <v>10</v>
@@ -72320,10 +72320,10 @@
         <v>6108</v>
       </c>
       <c r="F1160" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1160" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1160" s="15">
         <v>0</v>
@@ -72380,10 +72380,10 @@
         <v>6108</v>
       </c>
       <c r="F1161" s="15">
-        <v>0</v>
+        <v>6404</v>
       </c>
       <c r="G1161" s="15">
-        <v>6404</v>
+        <v>0</v>
       </c>
       <c r="H1161" s="15">
         <v>10</v>
@@ -72440,10 +72440,10 @@
         <v>6108</v>
       </c>
       <c r="F1162" s="15">
-        <v>0</v>
+        <v>6404</v>
       </c>
       <c r="G1162" s="15">
-        <v>6404</v>
+        <v>0</v>
       </c>
       <c r="H1162" s="15">
         <v>10</v>
@@ -72500,10 +72500,10 @@
         <v>6108</v>
       </c>
       <c r="F1163" s="15">
-        <v>0</v>
+        <v>6404</v>
       </c>
       <c r="G1163" s="15">
-        <v>6404</v>
+        <v>0</v>
       </c>
       <c r="H1163" s="15">
         <v>10</v>
@@ -72560,10 +72560,10 @@
         <v>5102</v>
       </c>
       <c r="F1164" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1164" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1164" s="15">
         <v>0</v>
@@ -72618,10 +72618,10 @@
         <v>6108</v>
       </c>
       <c r="F1165" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1165" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1165" s="15">
         <v>0</v>
@@ -72676,10 +72676,10 @@
         <v>6108</v>
       </c>
       <c r="F1166" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1166" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1166" s="15">
         <v>0</v>
@@ -72736,10 +72736,10 @@
         <v>6108</v>
       </c>
       <c r="F1167" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1167" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1167" s="15">
         <v>0</v>
@@ -72796,10 +72796,10 @@
         <v>6108</v>
       </c>
       <c r="F1168" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1168" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1168" s="15">
         <v>0</v>
@@ -72856,10 +72856,10 @@
         <v>6108</v>
       </c>
       <c r="F1169" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1169" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1169" s="15">
         <v>0</v>
@@ -72916,10 +72916,10 @@
         <v>6108</v>
       </c>
       <c r="F1170" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1170" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1170" s="15">
         <v>0</v>
@@ -72976,10 +72976,10 @@
         <v>6108</v>
       </c>
       <c r="F1171" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1171" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1171" s="15">
         <v>0</v>
@@ -73034,10 +73034,10 @@
         <v>6108</v>
       </c>
       <c r="F1172" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1172" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1172" s="15">
         <v>0</v>
@@ -73092,10 +73092,10 @@
         <v>6108</v>
       </c>
       <c r="F1173" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1173" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1173" s="15">
         <v>0</v>
@@ -73152,10 +73152,10 @@
         <v>5102</v>
       </c>
       <c r="F1174" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1174" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1174" s="15">
         <v>0</v>
@@ -73210,10 +73210,10 @@
         <v>6108</v>
       </c>
       <c r="F1175" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1175" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1175" s="15">
         <v>0</v>
@@ -73270,10 +73270,10 @@
         <v>6108</v>
       </c>
       <c r="F1176" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1176" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1176" s="15">
         <v>0</v>
@@ -73330,10 +73330,10 @@
         <v>6108</v>
       </c>
       <c r="F1177" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1177" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1177" s="15">
         <v>0</v>
@@ -73390,10 +73390,10 @@
         <v>6108</v>
       </c>
       <c r="F1178" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1178" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1178" s="15">
         <v>0</v>
@@ -73450,10 +73450,10 @@
         <v>6108</v>
       </c>
       <c r="F1179" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1179" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1179" s="15">
         <v>0</v>
@@ -73510,10 +73510,10 @@
         <v>6108</v>
       </c>
       <c r="F1180" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1180" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1180" s="15">
         <v>0</v>
@@ -73570,10 +73570,10 @@
         <v>5102</v>
       </c>
       <c r="F1181" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1181" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1181" s="15">
         <v>0</v>
@@ -73630,10 +73630,10 @@
         <v>6108</v>
       </c>
       <c r="F1182" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1182" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1182" s="15">
         <v>0</v>
@@ -73690,10 +73690,10 @@
         <v>6108</v>
       </c>
       <c r="F1183" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1183" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1183" s="15">
         <v>0</v>
@@ -73750,10 +73750,10 @@
         <v>6108</v>
       </c>
       <c r="F1184" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1184" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1184" s="15">
         <v>0</v>
@@ -73810,10 +73810,10 @@
         <v>6108</v>
       </c>
       <c r="F1185" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1185" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1185" s="15">
         <v>0</v>
@@ -73870,10 +73870,10 @@
         <v>6108</v>
       </c>
       <c r="F1186" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1186" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1186" s="15">
         <v>0</v>
@@ -73930,10 +73930,10 @@
         <v>5102</v>
       </c>
       <c r="F1187" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1187" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1187" s="15">
         <v>0</v>
@@ -73990,10 +73990,10 @@
         <v>6108</v>
       </c>
       <c r="F1188" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1188" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1188" s="15">
         <v>0</v>
@@ -74048,10 +74048,10 @@
         <v>6108</v>
       </c>
       <c r="F1189" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1189" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1189" s="15">
         <v>0</v>
@@ -74106,10 +74106,10 @@
         <v>6108</v>
       </c>
       <c r="F1190" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1190" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1190" s="15">
         <v>0</v>
@@ -74166,10 +74166,10 @@
         <v>5102</v>
       </c>
       <c r="F1191" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1191" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1191" s="15">
         <v>0</v>
@@ -74224,10 +74224,10 @@
         <v>6108</v>
       </c>
       <c r="F1192" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1192" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1192" s="15">
         <v>0</v>
@@ -74284,10 +74284,10 @@
         <v>6108</v>
       </c>
       <c r="F1193" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1193" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1193" s="15">
         <v>0</v>
@@ -74344,10 +74344,10 @@
         <v>6108</v>
       </c>
       <c r="F1194" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1194" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1194" s="15">
         <v>0</v>
@@ -74404,10 +74404,10 @@
         <v>6108</v>
       </c>
       <c r="F1195" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1195" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1195" s="15">
         <v>0</v>
@@ -74464,10 +74464,10 @@
         <v>6108</v>
       </c>
       <c r="F1196" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1196" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1196" s="15">
         <v>0</v>
@@ -74524,10 +74524,10 @@
         <v>6108</v>
       </c>
       <c r="F1197" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1197" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1197" s="15">
         <v>0</v>
@@ -74584,10 +74584,10 @@
         <v>5102</v>
       </c>
       <c r="F1198" s="15">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="G1198" s="15">
-        <v>5102</v>
+        <v>0</v>
       </c>
       <c r="H1198" s="15">
         <v>0</v>
@@ -74644,10 +74644,10 @@
         <v>5405</v>
       </c>
       <c r="F1199" s="15">
+        <v>5405</v>
+      </c>
+      <c r="G1199" s="15">
         <v>60</v>
-      </c>
-      <c r="G1199" s="15">
-        <v>5405</v>
       </c>
       <c r="H1199" s="15">
         <v>60</v>
@@ -74702,10 +74702,10 @@
         <v>6108</v>
       </c>
       <c r="F1200" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1200" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1200" s="15">
         <v>0</v>
@@ -74760,10 +74760,10 @@
         <v>6108</v>
       </c>
       <c r="F1201" s="15">
-        <v>0</v>
+        <v>6404</v>
       </c>
       <c r="G1201" s="15">
-        <v>6404</v>
+        <v>0</v>
       </c>
       <c r="H1201" s="15">
         <v>10</v>
@@ -74818,10 +74818,10 @@
         <v>6108</v>
       </c>
       <c r="F1202" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1202" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1202" s="15">
         <v>0</v>
@@ -74878,10 +74878,10 @@
         <v>6108</v>
       </c>
       <c r="F1203" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1203" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1203" s="15">
         <v>0</v>
@@ -74938,10 +74938,10 @@
         <v>6108</v>
       </c>
       <c r="F1204" s="15">
-        <v>0</v>
+        <v>6404</v>
       </c>
       <c r="G1204" s="15">
-        <v>6404</v>
+        <v>0</v>
       </c>
       <c r="H1204" s="15">
         <v>10</v>
@@ -74998,10 +74998,10 @@
         <v>6108</v>
       </c>
       <c r="F1205" s="15">
-        <v>0</v>
+        <v>6102</v>
       </c>
       <c r="G1205" s="15">
-        <v>6102</v>
+        <v>0</v>
       </c>
       <c r="H1205" s="15">
         <v>0</v>
@@ -75058,10 +75058,10 @@
         <v>6108</v>
       </c>
       <c r="F1206" s="15">
-        <v>0</v>
+        <v>6202</v>
       </c>
       <c r="G1206" s="15">
-        <v>6202</v>
+        <v>0</v>
       </c>
       <c r="H1206" s="15">
         <v>0</v>
@@ -75116,10 +75116,10 @@
         <v>5405</v>
       </c>
       <c r="F1207" s="15">
+        <v>5405</v>
+      </c>
+      <c r="G1207" s="15">
         <v>60</v>
-      </c>
-      <c r="G1207" s="15">
-        <v>5405</v>
       </c>
       <c r="H1207" s="15">
         <v>60</v>

--- a/conf_fiscais.xlsx
+++ b/conf_fiscais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Faturamento\Desktop\nfe_sistema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7012D63-CD94-4E70-BFFE-9C9238DB015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A84E98A-D38C-4BAE-9E2D-4B25FBC7AAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F76E099-F64F-4C5B-B230-95152170BA2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Config Fiscal" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="CFOP" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$1207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Config Fiscal'!$A$1:$T$1599</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Config ST'!$A$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45506,7 +45506,7 @@
         <v>0</v>
       </c>
       <c r="H751" s="13">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I751" s="13">
         <v>3</v>
@@ -96368,7 +96368,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1207" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
+  <autoFilter ref="A1:T1599" xr:uid="{F19E3CB5-90C7-45F0-9B94-7D51DC2930E8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
